--- a/excel_files/10.5.1.1.xlsx
+++ b/excel_files/10.5.1.1.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55F0DB6-016B-48AE-8CD7-86A13A78353B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>10.5.1.1 Показатели финансовой устойчивости*</t>
   </si>
@@ -316,16 +317,19 @@
       </rPr>
       <t xml:space="preserve"> excluding loans granted to banks and other financial and credit organizations</t>
     </r>
+  </si>
+  <si>
+    <t>предварительные данные</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -334,6 +338,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <name val="Times New Roman"/>
@@ -426,12 +438,18 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -463,65 +481,74 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{49AA7F5B-7FDF-47B2-B70F-B200575B29D8}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -537,9 +564,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -577,9 +604,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -614,7 +641,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -649,7 +676,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -822,18 +849,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="34.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -854,7 +881,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -879,7 +906,7 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
     </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="3"/>
       <c r="C3" s="2"/>
@@ -897,8 +924,9 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
+      <c r="U3" s="18"/>
     </row>
-    <row r="4" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -959,8 +987,11 @@
       <c r="T4" s="7">
         <v>2023</v>
       </c>
+      <c r="U4" s="7">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>8</v>
       </c>
@@ -1021,8 +1052,11 @@
       <c r="T5" s="11">
         <v>50</v>
       </c>
+      <c r="U5" s="19">
+        <v>53.5</v>
+      </c>
     </row>
-    <row r="6" spans="1:20" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>12</v>
       </c>
@@ -1083,8 +1117,11 @@
       <c r="T6" s="11">
         <v>35.1</v>
       </c>
+      <c r="U6" s="19">
+        <v>38.9</v>
+      </c>
     </row>
-    <row r="7" spans="1:20" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>15</v>
       </c>
@@ -1145,15 +1182,18 @@
       <c r="T7" s="13">
         <v>21</v>
       </c>
+      <c r="U7" s="20">
+        <v>22.4</v>
+      </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+    <row r="8" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="15" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="2"/>
@@ -1170,15 +1210,18 @@
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
+      <c r="U8" s="17" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="2"/>
@@ -1196,14 +1239,14 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+    <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="16" t="s">
         <v>27</v>
       </c>
       <c r="D10" s="2"/>
